--- a/data/DSUBICI/RIVADAVIA.xlsx
+++ b/data/DSUBICI/RIVADAVIA.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2591.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -522,7 +522,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1344.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1117.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -604,7 +604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1102.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1087.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>891.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -760,7 +760,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -799,7 +799,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>815.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>721.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>629.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>581.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>512.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>505.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>498.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>485.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>463.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>461.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>456.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>448.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>411.0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>401.0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3613.</t>
+          <t>3613.0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>341.0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>330.0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>314.0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>306.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>283.0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>264.0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>259.0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -3692,12 +3692,12 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ISABEL MARIA Y  LAURA VIÑAS</t>
+          <t>PROVINVEST</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>EXIMIA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#ffff00</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -7612,11 +7612,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9726,11 +9722,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12156,11 +12148,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12433,11 +12421,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -21080,11 +21064,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I526" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -21119,11 +21099,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I527" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -22562,11 +22538,7 @@
           <t>#00ff00</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -27772,11 +27744,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I698" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -28162,11 +28130,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I708" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -33357,11 +33321,7 @@
           <t>#ffffff</t>
         </is>
       </c>
-      <c r="I841" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -43543,11 +43503,7 @@
           <t>#ff0000</t>
         </is>
       </c>
-      <c r="I1103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
+      <c r="I1103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/DSUBICI/RIVADAVIA.xlsx
+++ b/data/DSUBICI/RIVADAVIA.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -14610,7 +14610,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -17921,7 +17921,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -18272,7 +18272,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -18311,7 +18311,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -18865,7 +18865,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -19103,7 +19103,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -19376,7 +19376,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -20589,7 +20589,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -20905,7 +20905,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I526" t="inlineStr"/>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I527" t="inlineStr"/>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -21170,7 +21170,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -21209,7 +21209,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -21404,7 +21404,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -21443,7 +21443,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -21638,7 +21638,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -21677,7 +21677,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -21833,7 +21833,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -21989,7 +21989,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -22028,7 +22028,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -22648,7 +22648,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -22765,7 +22765,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -22843,7 +22843,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -22882,7 +22882,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -22921,7 +22921,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -22960,7 +22960,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -22999,7 +22999,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -23194,7 +23194,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -23272,7 +23272,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -23467,7 +23467,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -23506,7 +23506,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -23623,7 +23623,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -23740,7 +23740,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -23779,7 +23779,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -23931,7 +23931,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -24165,7 +24165,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -24321,7 +24321,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -24399,7 +24399,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -24555,7 +24555,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -24633,7 +24633,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -24711,7 +24711,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -24867,7 +24867,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -25218,7 +25218,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -25335,7 +25335,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -25374,7 +25374,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -25413,7 +25413,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -25569,7 +25569,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -25608,7 +25608,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -25721,7 +25721,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -25877,7 +25877,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -25955,7 +25955,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -26111,7 +26111,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -26189,7 +26189,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -26228,7 +26228,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -26267,7 +26267,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -26380,7 +26380,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -26419,7 +26419,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -26458,7 +26458,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -26653,7 +26653,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -26692,7 +26692,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -26809,7 +26809,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -26965,7 +26965,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -27004,7 +27004,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -27199,7 +27199,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -27238,7 +27238,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -27351,7 +27351,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -27390,7 +27390,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -27468,7 +27468,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -27507,7 +27507,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -27585,7 +27585,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -27624,7 +27624,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I698" t="inlineStr"/>
@@ -27776,7 +27776,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -27815,7 +27815,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -27971,7 +27971,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -28010,7 +28010,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -28049,7 +28049,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -28088,7 +28088,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -28127,7 +28127,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I708" t="inlineStr"/>
@@ -28162,7 +28162,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -28201,7 +28201,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -28357,7 +28357,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -28396,7 +28396,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -28474,7 +28474,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -28513,7 +28513,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -28673,7 +28673,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -28790,7 +28790,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -28829,7 +28829,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -28868,7 +28868,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -28907,7 +28907,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -28946,7 +28946,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -28985,7 +28985,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -29258,7 +29258,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -29570,7 +29570,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -29609,7 +29609,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -29687,7 +29687,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -29765,7 +29765,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -29804,7 +29804,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -29882,7 +29882,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -29921,7 +29921,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -29960,7 +29960,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -29999,7 +29999,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -30038,7 +30038,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -30194,7 +30194,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -30237,7 +30237,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -30315,7 +30315,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -30354,7 +30354,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -30510,7 +30510,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -30588,7 +30588,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -30627,7 +30627,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -30666,7 +30666,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -30783,7 +30783,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -30861,7 +30861,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -30900,7 +30900,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -30939,7 +30939,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -30978,7 +30978,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -31056,7 +31056,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -31173,7 +31173,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -31212,7 +31212,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -31329,7 +31329,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -31368,7 +31368,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -31407,7 +31407,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -31680,7 +31680,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -31719,7 +31719,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -31758,7 +31758,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -31836,7 +31836,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -31914,7 +31914,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -31953,7 +31953,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -31992,7 +31992,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -32031,7 +32031,7 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -32070,7 +32070,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -32187,7 +32187,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -32226,7 +32226,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -32304,7 +32304,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -32343,7 +32343,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -32382,7 +32382,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -32421,7 +32421,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -32499,7 +32499,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -32538,7 +32538,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -32577,7 +32577,7 @@
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
@@ -32616,7 +32616,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
@@ -32694,7 +32694,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -32733,7 +32733,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
@@ -32889,7 +32889,7 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
@@ -32967,7 +32967,7 @@
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
@@ -33006,7 +33006,7 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -33045,7 +33045,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -33084,7 +33084,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I837" t="inlineStr">
@@ -33201,7 +33201,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -33240,7 +33240,7 @@
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
@@ -33318,7 +33318,7 @@
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I841" t="inlineStr"/>
@@ -33353,7 +33353,7 @@
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
@@ -33392,7 +33392,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -33431,7 +33431,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -33470,7 +33470,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -33509,7 +33509,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -33587,7 +33587,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -33704,7 +33704,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -33743,7 +33743,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -33782,7 +33782,7 @@
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I858" t="inlineStr">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -34055,7 +34055,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -34094,7 +34094,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -34133,7 +34133,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -34211,7 +34211,7 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">
@@ -34324,7 +34324,7 @@
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
@@ -34402,7 +34402,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -34441,7 +34441,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -34519,7 +34519,7 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -34558,7 +34558,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -34597,7 +34597,7 @@
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -34636,7 +34636,7 @@
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -34675,7 +34675,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -34714,7 +34714,7 @@
       </c>
       <c r="H877" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -34753,7 +34753,7 @@
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -34792,7 +34792,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -34870,7 +34870,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -34948,7 +34948,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -34987,7 +34987,7 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -35065,7 +35065,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -35143,7 +35143,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -35182,7 +35182,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -35221,7 +35221,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -35260,7 +35260,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
@@ -35338,7 +35338,7 @@
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
@@ -35377,7 +35377,7 @@
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
@@ -35494,7 +35494,7 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
@@ -35533,7 +35533,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -35650,7 +35650,7 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -35689,7 +35689,7 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -35724,7 +35724,7 @@
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -35763,7 +35763,7 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -35841,7 +35841,7 @@
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -35919,7 +35919,7 @@
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -36036,7 +36036,7 @@
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
@@ -36153,7 +36153,7 @@
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
@@ -36231,7 +36231,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -36309,7 +36309,7 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
@@ -36387,7 +36387,7 @@
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -36465,7 +36465,7 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -36504,7 +36504,7 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -36582,7 +36582,7 @@
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I927" t="inlineStr">
@@ -36699,7 +36699,7 @@
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
@@ -36777,7 +36777,7 @@
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
@@ -36816,7 +36816,7 @@
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
@@ -36855,7 +36855,7 @@
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
@@ -36894,7 +36894,7 @@
       </c>
       <c r="H933" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I933" t="inlineStr">
@@ -36933,7 +36933,7 @@
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -36972,7 +36972,7 @@
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
@@ -37050,7 +37050,7 @@
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I937" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I938" t="inlineStr">
@@ -37128,7 +37128,7 @@
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -37206,7 +37206,7 @@
       </c>
       <c r="H941" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I941" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
@@ -37284,7 +37284,7 @@
       </c>
       <c r="H943" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I943" t="inlineStr">
@@ -37323,7 +37323,7 @@
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
@@ -37362,7 +37362,7 @@
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
@@ -37440,7 +37440,7 @@
       </c>
       <c r="H947" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I947" t="inlineStr">
@@ -37479,7 +37479,7 @@
       </c>
       <c r="H948" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I948" t="inlineStr">
@@ -37518,7 +37518,7 @@
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I949" t="inlineStr">
@@ -37557,7 +37557,7 @@
       </c>
       <c r="H950" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I950" t="inlineStr">
@@ -37596,7 +37596,7 @@
       </c>
       <c r="H951" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I951" t="inlineStr">
@@ -37635,7 +37635,7 @@
       </c>
       <c r="H952" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I952" t="inlineStr">
@@ -37674,7 +37674,7 @@
       </c>
       <c r="H953" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I953" t="inlineStr">
@@ -37713,7 +37713,7 @@
       </c>
       <c r="H954" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I954" t="inlineStr">
@@ -37752,7 +37752,7 @@
       </c>
       <c r="H955" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I955" t="inlineStr">
@@ -37791,7 +37791,7 @@
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
@@ -37830,7 +37830,7 @@
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
@@ -37869,7 +37869,7 @@
       </c>
       <c r="H958" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I958" t="inlineStr">
@@ -37908,7 +37908,7 @@
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
@@ -37947,7 +37947,7 @@
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
@@ -38025,7 +38025,7 @@
       </c>
       <c r="H962" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
@@ -38064,7 +38064,7 @@
       </c>
       <c r="H963" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I963" t="inlineStr">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -38142,7 +38142,7 @@
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
@@ -38181,7 +38181,7 @@
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
@@ -38220,7 +38220,7 @@
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
@@ -38259,7 +38259,7 @@
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I968" t="inlineStr">
@@ -38337,7 +38337,7 @@
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
@@ -38376,7 +38376,7 @@
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
@@ -38493,7 +38493,7 @@
       </c>
       <c r="H974" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
@@ -38532,7 +38532,7 @@
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
@@ -38571,7 +38571,7 @@
       </c>
       <c r="H976" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
@@ -38610,7 +38610,7 @@
       </c>
       <c r="H977" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I977" t="inlineStr">
@@ -38649,7 +38649,7 @@
       </c>
       <c r="H978" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I978" t="inlineStr">
@@ -38688,7 +38688,7 @@
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
@@ -38727,7 +38727,7 @@
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
@@ -38766,7 +38766,7 @@
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
@@ -38844,7 +38844,7 @@
       </c>
       <c r="H983" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I983" t="inlineStr">
@@ -38883,7 +38883,7 @@
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="H985" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -38961,7 +38961,7 @@
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
@@ -39000,7 +39000,7 @@
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="H988" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I988" t="inlineStr">
@@ -39078,7 +39078,7 @@
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="H990" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I990" t="inlineStr">
@@ -39195,7 +39195,7 @@
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
@@ -39234,7 +39234,7 @@
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
@@ -39273,7 +39273,7 @@
       </c>
       <c r="H994" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I994" t="inlineStr">
@@ -39351,7 +39351,7 @@
       </c>
       <c r="H996" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I996" t="inlineStr">
@@ -39390,7 +39390,7 @@
       </c>
       <c r="H997" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
@@ -39429,7 +39429,7 @@
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -39464,7 +39464,7 @@
       </c>
       <c r="H999" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I999" t="inlineStr">
@@ -39503,7 +39503,7 @@
       </c>
       <c r="H1000" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1000" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="H1001" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1001" t="inlineStr">
@@ -39581,7 +39581,7 @@
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -39620,7 +39620,7 @@
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -39659,7 +39659,7 @@
       </c>
       <c r="H1004" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1004" t="inlineStr">
@@ -39698,7 +39698,7 @@
       </c>
       <c r="H1005" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1005" t="inlineStr">
@@ -39737,7 +39737,7 @@
       </c>
       <c r="H1006" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1006" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -39815,7 +39815,7 @@
       </c>
       <c r="H1008" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1008" t="inlineStr">
@@ -39854,7 +39854,7 @@
       </c>
       <c r="H1009" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1009" t="inlineStr">
@@ -39893,7 +39893,7 @@
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
@@ -39932,7 +39932,7 @@
       </c>
       <c r="H1011" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1011" t="inlineStr">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -40006,7 +40006,7 @@
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
@@ -40045,7 +40045,7 @@
       </c>
       <c r="H1014" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
@@ -40084,7 +40084,7 @@
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
@@ -40201,7 +40201,7 @@
       </c>
       <c r="H1018" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
@@ -40240,7 +40240,7 @@
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
@@ -40279,7 +40279,7 @@
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
@@ -40318,7 +40318,7 @@
       </c>
       <c r="H1021" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1021" t="inlineStr">
@@ -40357,7 +40357,7 @@
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
@@ -40396,7 +40396,7 @@
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
@@ -40435,7 +40435,7 @@
       </c>
       <c r="H1024" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1024" t="inlineStr">
@@ -40474,7 +40474,7 @@
       </c>
       <c r="H1025" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1025" t="inlineStr">
@@ -40513,7 +40513,7 @@
       </c>
       <c r="H1026" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1026" t="inlineStr">
@@ -40552,7 +40552,7 @@
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
@@ -40591,7 +40591,7 @@
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
@@ -40669,7 +40669,7 @@
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
@@ -40704,7 +40704,7 @@
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
@@ -40743,7 +40743,7 @@
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1032" t="inlineStr">
@@ -40782,7 +40782,7 @@
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
@@ -40821,7 +40821,7 @@
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
@@ -40899,7 +40899,7 @@
       </c>
       <c r="H1036" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1036" t="inlineStr">
@@ -40938,7 +40938,7 @@
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
@@ -40977,7 +40977,7 @@
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1038" t="inlineStr">
@@ -41016,7 +41016,7 @@
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1039" t="inlineStr">
@@ -41055,7 +41055,7 @@
       </c>
       <c r="H1040" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1040" t="inlineStr">
@@ -41094,7 +41094,7 @@
       </c>
       <c r="H1041" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1041" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="H1042" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1042" t="inlineStr">
@@ -41172,7 +41172,7 @@
       </c>
       <c r="H1043" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1043" t="inlineStr">
@@ -41211,7 +41211,7 @@
       </c>
       <c r="H1044" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1044" t="inlineStr">
@@ -41250,7 +41250,7 @@
       </c>
       <c r="H1045" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1045" t="inlineStr">
@@ -41289,7 +41289,7 @@
       </c>
       <c r="H1046" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1046" t="inlineStr">
@@ -41367,7 +41367,7 @@
       </c>
       <c r="H1048" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1048" t="inlineStr">
@@ -41406,7 +41406,7 @@
       </c>
       <c r="H1049" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1049" t="inlineStr">
@@ -41445,7 +41445,7 @@
       </c>
       <c r="H1050" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1050" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1051" t="inlineStr">
@@ -41523,7 +41523,7 @@
       </c>
       <c r="H1052" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1052" t="inlineStr">
@@ -41562,7 +41562,7 @@
       </c>
       <c r="H1053" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1053" t="inlineStr">
@@ -41597,7 +41597,7 @@
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1054" t="inlineStr">
@@ -41636,7 +41636,7 @@
       </c>
       <c r="H1055" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
@@ -41675,7 +41675,7 @@
       </c>
       <c r="H1056" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
@@ -41714,7 +41714,7 @@
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
@@ -41753,7 +41753,7 @@
       </c>
       <c r="H1058" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1058" t="inlineStr">
@@ -41792,7 +41792,7 @@
       </c>
       <c r="H1059" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1059" t="inlineStr">
@@ -41831,7 +41831,7 @@
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
@@ -41870,7 +41870,7 @@
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
@@ -41909,7 +41909,7 @@
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
@@ -41948,7 +41948,7 @@
       </c>
       <c r="H1063" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
@@ -41987,7 +41987,7 @@
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1064" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
@@ -42065,7 +42065,7 @@
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="H1067" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1067" t="inlineStr">
@@ -42143,7 +42143,7 @@
       </c>
       <c r="H1068" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1068" t="inlineStr">
@@ -42182,7 +42182,7 @@
       </c>
       <c r="H1069" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1069" t="inlineStr">
@@ -42260,7 +42260,7 @@
       </c>
       <c r="H1071" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1071" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="H1072" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1072" t="inlineStr">
@@ -42338,7 +42338,7 @@
       </c>
       <c r="H1073" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1073" t="inlineStr">
@@ -42377,7 +42377,7 @@
       </c>
       <c r="H1074" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1074" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="H1075" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1075" t="inlineStr">
@@ -42455,7 +42455,7 @@
       </c>
       <c r="H1076" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1076" t="inlineStr">
@@ -42494,7 +42494,7 @@
       </c>
       <c r="H1077" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1077" t="inlineStr">
@@ -42533,7 +42533,7 @@
       </c>
       <c r="H1078" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1078" t="inlineStr">
@@ -42572,7 +42572,7 @@
       </c>
       <c r="H1079" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1079" t="inlineStr">
@@ -42611,7 +42611,7 @@
       </c>
       <c r="H1080" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1080" t="inlineStr">
@@ -42650,7 +42650,7 @@
       </c>
       <c r="H1081" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1081" t="inlineStr">
@@ -42689,7 +42689,7 @@
       </c>
       <c r="H1082" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1082" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="H1083" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1083" t="inlineStr">
@@ -42767,7 +42767,7 @@
       </c>
       <c r="H1084" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1084" t="inlineStr">
@@ -42806,7 +42806,7 @@
       </c>
       <c r="H1085" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1085" t="inlineStr">
@@ -42845,7 +42845,7 @@
       </c>
       <c r="H1086" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1086" t="inlineStr">
@@ -42923,7 +42923,7 @@
       </c>
       <c r="H1088" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1088" t="inlineStr">
@@ -42962,7 +42962,7 @@
       </c>
       <c r="H1089" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
@@ -43001,7 +43001,7 @@
       </c>
       <c r="H1090" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1090" t="inlineStr">
@@ -43040,7 +43040,7 @@
       </c>
       <c r="H1091" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="H1092" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1092" t="inlineStr">
@@ -43118,7 +43118,7 @@
       </c>
       <c r="H1093" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1093" t="inlineStr">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="H1094" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1094" t="inlineStr">
@@ -43196,7 +43196,7 @@
       </c>
       <c r="H1095" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1095" t="inlineStr">
@@ -43235,7 +43235,7 @@
       </c>
       <c r="H1096" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1096" t="inlineStr">
@@ -43274,7 +43274,7 @@
       </c>
       <c r="H1097" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1097" t="inlineStr">
@@ -43313,7 +43313,7 @@
       </c>
       <c r="H1098" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1098" t="inlineStr">
@@ -43352,7 +43352,7 @@
       </c>
       <c r="H1099" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1099" t="inlineStr">
@@ -43391,7 +43391,7 @@
       </c>
       <c r="H1100" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1100" t="inlineStr">
@@ -43461,7 +43461,7 @@
       </c>
       <c r="H1102" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>transparent</t>
         </is>
       </c>
       <c r="I1102" t="inlineStr">
@@ -43500,7 +43500,7 @@
       </c>
       <c r="H1103" t="inlineStr">
         <is>
-          <t>#ff0000</t>
+          <t>#00ffff</t>
         </is>
       </c>
       <c r="I1103" t="inlineStr"/>
